--- a/exercise/Admin/Admin Desa/Tes Excel Administrasi Desa.xlsx
+++ b/exercise/Admin/Admin Desa/Tes Excel Administrasi Desa.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Buat Youtube\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Desa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6EB848-70B4-4189-8CA4-D46A42C89AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4F395A-4D04-42A8-A5EC-3B564E704219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11070" tabRatio="599" xr2:uid="{3FDB169C-B558-497A-A591-5CB360CCCFEA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" tabRatio="599" xr2:uid="{3FDB169C-B558-497A-A591-5CB360CCCFEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,7 +23,9 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -134,8 +136,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
+  <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
@@ -250,13 +251,12 @@
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -265,9 +265,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -275,8 +272,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -290,16 +285,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -309,17 +304,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -653,12 +647,12 @@
     <col min="2" max="2" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" style="5" customWidth="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8" style="5" customWidth="1"/>
+    <col min="10" max="10" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.85546875" style="1" customWidth="1"/>
     <col min="12" max="12" width="14.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="2.42578125" style="1" customWidth="1"/>
@@ -670,426 +664,738 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="11"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="9"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="N3" s="26" t="s">
+      <c r="E3" s="15">
+        <f>INDEX($O$5:$O$7,MATCH(C3,$N$5:$N$7))</f>
+        <v>5000000</v>
+      </c>
+      <c r="F3" s="15">
+        <f>INDEX($P$5:$P$7,MATCH(C3,$N$5:$N$7))</f>
+        <v>500000</v>
+      </c>
+      <c r="G3" s="15">
+        <f>INDEX($Q$5:$Q$7,MATCH(C3,$N$5:$N$7))</f>
+        <v>200000</v>
+      </c>
+      <c r="H3" s="16">
+        <f>SUM(E3:G3)</f>
+        <v>5700000</v>
+      </c>
+      <c r="I3" s="16">
+        <f>INDEX($O$11:$Q$11,MATCH(C3,$O$10:$Q$10))</f>
+        <v>125000</v>
+      </c>
+      <c r="J3" s="17">
+        <f>HLOOKUP(C3,$N$10:$Q$13,3,FALSE)*H3</f>
+        <v>570000</v>
+      </c>
+      <c r="K3" s="17">
+        <f>INDEX($O$13:$Q$13,MATCH(C3,$O$10:$Q$10))*H3</f>
+        <v>285000</v>
+      </c>
+      <c r="L3" s="17">
+        <f>H3-SUM(I3:K3)</f>
+        <v>4720000</v>
+      </c>
+      <c r="N3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="O3" s="26"/>
+      <c r="O3" s="22"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="12"/>
-      <c r="N4" s="7" t="s">
+      <c r="E4" s="15">
+        <f t="shared" ref="E4:E14" si="0">INDEX($O$5:$O$7,MATCH(C4,$N$5:$N$7))</f>
+        <v>4000000</v>
+      </c>
+      <c r="F4" s="15">
+        <f t="shared" ref="F4:F15" si="1">INDEX($P$5:$P$7,MATCH(C4,$N$5:$N$7))</f>
+        <v>400000</v>
+      </c>
+      <c r="G4" s="15">
+        <f t="shared" ref="G4:G15" si="2">INDEX($Q$5:$Q$7,MATCH(C4,$N$5:$N$7))</f>
+        <v>150000</v>
+      </c>
+      <c r="H4" s="16">
+        <f t="shared" ref="H4:H15" si="3">SUM(E4:G4)</f>
+        <v>4550000</v>
+      </c>
+      <c r="I4" s="16">
+        <f t="shared" ref="I4:I15" si="4">INDEX($O$11:$Q$11,MATCH(C4,$O$10:$Q$10))</f>
+        <v>100000</v>
+      </c>
+      <c r="J4" s="17">
+        <f t="shared" ref="J4:J15" si="5">HLOOKUP(C4,$N$10:$Q$13,3,FALSE)*H4</f>
+        <v>455000</v>
+      </c>
+      <c r="K4" s="17">
+        <f t="shared" ref="K4:K15" si="6">INDEX($O$13:$Q$13,MATCH(C4,$O$10:$Q$10))*H4</f>
+        <v>182000</v>
+      </c>
+      <c r="L4" s="17">
+        <f t="shared" ref="L4:L15" si="7">H4-SUM(I4:K4)</f>
+        <v>3813000</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="Q4" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="12"/>
-      <c r="N5" s="4" t="s">
+      <c r="E5" s="15">
+        <f t="shared" si="0"/>
+        <v>3000000</v>
+      </c>
+      <c r="F5" s="15">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+      <c r="G5" s="15">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="H5" s="16">
+        <f t="shared" si="3"/>
+        <v>3400000</v>
+      </c>
+      <c r="I5" s="16">
+        <f t="shared" si="4"/>
+        <v>50000</v>
+      </c>
+      <c r="J5" s="17">
+        <f t="shared" si="5"/>
+        <v>340000</v>
+      </c>
+      <c r="K5" s="17">
+        <f t="shared" si="6"/>
+        <v>102000</v>
+      </c>
+      <c r="L5" s="17">
+        <f t="shared" si="7"/>
+        <v>2908000</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O5" s="8">
         <v>5000000</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="8">
         <v>500000</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="8">
         <v>200000</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="12"/>
-      <c r="N6" s="4" t="s">
+      <c r="E6" s="15">
+        <f t="shared" si="0"/>
+        <v>3000000</v>
+      </c>
+      <c r="F6" s="15">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="H6" s="16">
+        <f t="shared" si="3"/>
+        <v>3400000</v>
+      </c>
+      <c r="I6" s="16">
+        <f t="shared" si="4"/>
+        <v>50000</v>
+      </c>
+      <c r="J6" s="17">
+        <f t="shared" si="5"/>
+        <v>340000</v>
+      </c>
+      <c r="K6" s="17">
+        <f t="shared" si="6"/>
+        <v>102000</v>
+      </c>
+      <c r="L6" s="17">
+        <f t="shared" si="7"/>
+        <v>2908000</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O6" s="8">
         <v>4000000</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="8">
         <v>400000</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="Q6" s="8">
         <v>150000</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="12"/>
-      <c r="N7" s="4" t="s">
+      <c r="E7" s="15">
+        <f t="shared" si="0"/>
+        <v>4000000</v>
+      </c>
+      <c r="F7" s="15">
+        <f t="shared" si="1"/>
+        <v>400000</v>
+      </c>
+      <c r="G7" s="15">
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="H7" s="16">
+        <f t="shared" si="3"/>
+        <v>4550000</v>
+      </c>
+      <c r="I7" s="16">
+        <f t="shared" si="4"/>
+        <v>100000</v>
+      </c>
+      <c r="J7" s="17">
+        <f t="shared" si="5"/>
+        <v>455000</v>
+      </c>
+      <c r="K7" s="17">
+        <f t="shared" si="6"/>
+        <v>182000</v>
+      </c>
+      <c r="L7" s="17">
+        <f t="shared" si="7"/>
+        <v>3813000</v>
+      </c>
+      <c r="N7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="O7" s="10">
+      <c r="O7" s="8">
         <v>3000000</v>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="8">
         <v>300000</v>
       </c>
-      <c r="Q7" s="10">
+      <c r="Q7" s="8">
         <v>100000</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>6</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="12"/>
+      <c r="E8" s="15">
+        <f t="shared" si="0"/>
+        <v>5000000</v>
+      </c>
+      <c r="F8" s="15">
+        <f t="shared" si="1"/>
+        <v>500000</v>
+      </c>
+      <c r="G8" s="15">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+      <c r="H8" s="16">
+        <f t="shared" si="3"/>
+        <v>5700000</v>
+      </c>
+      <c r="I8" s="16">
+        <f t="shared" si="4"/>
+        <v>125000</v>
+      </c>
+      <c r="J8" s="17">
+        <f t="shared" si="5"/>
+        <v>570000</v>
+      </c>
+      <c r="K8" s="17">
+        <f t="shared" si="6"/>
+        <v>285000</v>
+      </c>
+      <c r="L8" s="17">
+        <f t="shared" si="7"/>
+        <v>4720000</v>
+      </c>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>7</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="12"/>
-      <c r="N9" s="27" t="s">
+      <c r="E9" s="15">
+        <f t="shared" si="0"/>
+        <v>4000000</v>
+      </c>
+      <c r="F9" s="15">
+        <f t="shared" si="1"/>
+        <v>400000</v>
+      </c>
+      <c r="G9" s="15">
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="H9" s="16">
+        <f t="shared" si="3"/>
+        <v>4550000</v>
+      </c>
+      <c r="I9" s="16">
+        <f t="shared" si="4"/>
+        <v>100000</v>
+      </c>
+      <c r="J9" s="17">
+        <f t="shared" si="5"/>
+        <v>455000</v>
+      </c>
+      <c r="K9" s="17">
+        <f t="shared" si="6"/>
+        <v>182000</v>
+      </c>
+      <c r="L9" s="17">
+        <f t="shared" si="7"/>
+        <v>3813000</v>
+      </c>
+      <c r="N9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>8</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="12"/>
-      <c r="N10" s="7" t="s">
+      <c r="E10" s="15">
+        <f t="shared" si="0"/>
+        <v>3000000</v>
+      </c>
+      <c r="F10" s="15">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+      <c r="G10" s="15">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="H10" s="16">
+        <f t="shared" si="3"/>
+        <v>3400000</v>
+      </c>
+      <c r="I10" s="16">
+        <f t="shared" si="4"/>
+        <v>50000</v>
+      </c>
+      <c r="J10" s="17">
+        <f t="shared" si="5"/>
+        <v>340000</v>
+      </c>
+      <c r="K10" s="17">
+        <f t="shared" si="6"/>
+        <v>102000</v>
+      </c>
+      <c r="L10" s="17">
+        <f t="shared" si="7"/>
+        <v>2908000</v>
+      </c>
+      <c r="N10" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="O10" s="8" t="s">
+      <c r="O10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="P10" s="8" t="s">
+      <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="8" t="s">
+      <c r="Q10" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="12"/>
-      <c r="N11" s="17" t="s">
+      <c r="E11" s="15">
+        <f t="shared" si="0"/>
+        <v>3000000</v>
+      </c>
+      <c r="F11" s="15">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+      <c r="G11" s="15">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="H11" s="16">
+        <f t="shared" si="3"/>
+        <v>3400000</v>
+      </c>
+      <c r="I11" s="16">
+        <f t="shared" si="4"/>
+        <v>50000</v>
+      </c>
+      <c r="J11" s="17">
+        <f t="shared" si="5"/>
+        <v>340000</v>
+      </c>
+      <c r="K11" s="17">
+        <f t="shared" si="6"/>
+        <v>102000</v>
+      </c>
+      <c r="L11" s="17">
+        <f t="shared" si="7"/>
+        <v>2908000</v>
+      </c>
+      <c r="N11" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="O11" s="10">
+      <c r="O11" s="8">
         <v>125000</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="8">
         <v>100000</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="Q11" s="8">
         <v>50000</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>10</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="12"/>
-      <c r="N12" s="17" t="s">
+      <c r="E12" s="15">
+        <f t="shared" si="0"/>
+        <v>4000000</v>
+      </c>
+      <c r="F12" s="15">
+        <f t="shared" si="1"/>
+        <v>400000</v>
+      </c>
+      <c r="G12" s="15">
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="H12" s="16">
+        <f t="shared" si="3"/>
+        <v>4550000</v>
+      </c>
+      <c r="I12" s="16">
+        <f t="shared" si="4"/>
+        <v>100000</v>
+      </c>
+      <c r="J12" s="17">
+        <f t="shared" si="5"/>
+        <v>455000</v>
+      </c>
+      <c r="K12" s="17">
+        <f t="shared" si="6"/>
+        <v>182000</v>
+      </c>
+      <c r="L12" s="17">
+        <f t="shared" si="7"/>
+        <v>3813000</v>
+      </c>
+      <c r="N12" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="7">
         <v>0.1</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="7">
         <v>0.1</v>
       </c>
-      <c r="Q12" s="9">
+      <c r="Q12" s="7">
         <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>11</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="12"/>
-      <c r="N13" s="17" t="s">
+      <c r="E13" s="15">
+        <f t="shared" si="0"/>
+        <v>5000000</v>
+      </c>
+      <c r="F13" s="15">
+        <f t="shared" si="1"/>
+        <v>500000</v>
+      </c>
+      <c r="G13" s="15">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+      <c r="H13" s="16">
+        <f t="shared" si="3"/>
+        <v>5700000</v>
+      </c>
+      <c r="I13" s="16">
+        <f t="shared" si="4"/>
+        <v>125000</v>
+      </c>
+      <c r="J13" s="17">
+        <f t="shared" si="5"/>
+        <v>570000</v>
+      </c>
+      <c r="K13" s="17">
+        <f t="shared" si="6"/>
+        <v>285000</v>
+      </c>
+      <c r="L13" s="17">
+        <f t="shared" si="7"/>
+        <v>4720000</v>
+      </c>
+      <c r="N13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="7">
         <v>0.05</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P13" s="7">
         <v>0.04</v>
       </c>
-      <c r="Q13" s="9">
+      <c r="Q13" s="7">
         <v>0.03</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>12</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="18"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="12"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
+      <c r="E14" s="15">
+        <f t="shared" si="0"/>
+        <v>4000000</v>
+      </c>
+      <c r="F14" s="15">
+        <f t="shared" si="1"/>
+        <v>400000</v>
+      </c>
+      <c r="G14" s="15">
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="H14" s="16">
+        <f t="shared" si="3"/>
+        <v>4550000</v>
+      </c>
+      <c r="I14" s="16">
+        <f t="shared" si="4"/>
+        <v>100000</v>
+      </c>
+      <c r="J14" s="17">
+        <f t="shared" si="5"/>
+        <v>455000</v>
+      </c>
+      <c r="K14" s="17">
+        <f t="shared" si="6"/>
+        <v>182000</v>
+      </c>
+      <c r="L14" s="17">
+        <f t="shared" si="7"/>
+        <v>3813000</v>
+      </c>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="4">
+      <c r="B15" s="3">
         <v>13</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="12"/>
+      <c r="E15" s="15">
+        <f t="shared" ref="E4:E15" si="8">INDEX($O$5:$O$7,MATCH(C15,$N$5:$N$7))</f>
+        <v>3000000</v>
+      </c>
+      <c r="F15" s="15">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+      <c r="G15" s="15">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="H15" s="16">
+        <f t="shared" si="3"/>
+        <v>3400000</v>
+      </c>
+      <c r="I15" s="16">
+        <f t="shared" si="4"/>
+        <v>50000</v>
+      </c>
+      <c r="J15" s="17">
+        <f t="shared" si="5"/>
+        <v>340000</v>
+      </c>
+      <c r="K15" s="17">
+        <f t="shared" si="6"/>
+        <v>102000</v>
+      </c>
+      <c r="L15" s="17">
+        <f t="shared" si="7"/>
+        <v>2908000</v>
+      </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="30" t="s">
+      <c r="F16" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="5">
